--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-Reply.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-Reply.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="420">
   <si>
     <t>Property</t>
   </si>
@@ -496,6 +496,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Communication.meta.tag</t>
   </si>
   <si>
@@ -665,6 +672,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -678,6 +688,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -719,7 +732,14 @@
     <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.basedOn.id</t>
@@ -816,6 +836,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -891,6 +914,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -943,6 +969,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1220,9 +1249,6 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Erweiterungen werden immer (mindestens) nach url gesliced.</t>
-  </si>
-  <si>
     <t>Communication.payload.extension:OfferedSupplyOptions</t>
   </si>
   <si>
@@ -1242,10 +1268,6 @@
     <t>Sowohl Patient als auch Apotheke können ihre Lieferoptionen oder Angebote für die Abgabe von Medikamenten angeben.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Communication.payload.extension:AvailabilityStatus</t>
   </si>
   <si>
@@ -1301,7 +1323,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1649,7 +1677,7 @@
     <col min="26" max="26" width="52.72265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="49.6328125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.7421875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1658,7 +1686,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2982,7 +3010,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>98</v>
@@ -2994,15 +3022,15 @@
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3028,13 +3056,13 @@
         <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3060,13 +3088,13 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -3084,7 +3112,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3093,7 +3121,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>98</v>
@@ -3105,15 +3133,15 @@
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3139,13 +3167,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3195,7 +3223,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3221,10 +3249,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3247,16 +3275,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3282,13 +3310,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -3306,7 +3334,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3332,14 +3360,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3358,16 +3386,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3417,7 +3445,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3438,19 +3466,19 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3469,16 +3497,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3528,7 +3556,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3549,15 +3577,15 @@
         <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3586,7 +3614,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3627,19 +3655,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3660,15 +3688,15 @@
         <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3694,16 +3722,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3740,19 +3768,19 @@
         <v>76</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3773,15 +3801,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3804,19 +3832,19 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3865,7 +3893,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3874,27 +3902,27 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>76</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3917,15 +3945,17 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3974,7 +4004,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3989,21 +4019,21 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4029,13 +4059,13 @@
         <v>128</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4085,7 +4115,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4100,25 +4130,25 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4137,16 +4167,16 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4196,7 +4226,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4205,27 +4235,27 @@
         <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4331,10 +4361,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4442,10 +4472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4471,13 +4501,13 @@
         <v>100</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4527,7 +4557,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4536,7 +4566,7 @@
         <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>98</v>
@@ -4548,15 +4578,15 @@
         <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4582,13 +4612,13 @@
         <v>128</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4617,10 +4647,10 @@
         <v>150</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4638,7 +4668,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4659,15 +4689,15 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4690,16 +4720,16 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4749,7 +4779,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4758,7 +4788,7 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>98</v>
@@ -4770,15 +4800,15 @@
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4804,13 +4834,13 @@
         <v>100</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4860,7 +4890,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4881,19 +4911,19 @@
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4912,15 +4942,17 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4969,7 +5001,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4978,27 +5010,27 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5021,15 +5053,17 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5078,7 +5112,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5087,10 +5121,10 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>76</v>
@@ -5099,15 +5133,15 @@
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5130,16 +5164,16 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5147,7 +5181,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>76</v>
@@ -5165,31 +5199,31 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="Z32" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>86</v>
@@ -5204,10 +5238,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5215,14 +5249,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5241,16 +5275,16 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5276,31 +5310,31 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="Z33" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5309,27 +5343,27 @@
         <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>76</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5352,16 +5386,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5387,13 +5421,13 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5411,7 +5445,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5420,7 +5454,7 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>98</v>
@@ -5429,18 +5463,18 @@
         <v>76</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>76</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5463,23 +5497,23 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q35" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="R35" t="s" s="2">
         <v>76</v>
@@ -5500,13 +5534,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5524,7 +5558,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5542,7 +5576,7 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>76</v>
@@ -5550,10 +5584,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5576,15 +5610,17 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -5609,13 +5645,13 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5633,7 +5669,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5642,7 +5678,7 @@
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>98</v>
@@ -5654,19 +5690,19 @@
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>76</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5685,15 +5721,17 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5742,7 +5780,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5751,27 +5789,27 @@
         <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5794,16 +5832,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5829,13 +5867,13 @@
         <v>76</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>76</v>
@@ -5853,7 +5891,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5862,7 +5900,7 @@
         <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>98</v>
@@ -5871,18 +5909,18 @@
         <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>76</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5905,16 +5943,16 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5964,7 +6002,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5973,27 +6011,27 @@
         <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6016,16 +6054,16 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6075,7 +6113,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6084,27 +6122,27 @@
         <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6127,16 +6165,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6186,7 +6224,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6201,10 +6239,10 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6212,10 +6250,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6238,16 +6276,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6297,7 +6335,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6312,10 +6350,10 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6323,10 +6361,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6349,16 +6387,16 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6408,7 +6446,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6417,27 +6455,27 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6543,10 +6581,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6654,10 +6692,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6683,13 +6721,13 @@
         <v>100</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6739,7 +6777,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6748,7 +6786,7 @@
         <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>98</v>
@@ -6760,15 +6798,15 @@
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6794,13 +6832,13 @@
         <v>128</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6829,10 +6867,10 @@
         <v>150</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6850,7 +6888,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6871,15 +6909,15 @@
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6902,16 +6940,16 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6961,7 +6999,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6970,7 +7008,7 @@
         <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
@@ -6982,15 +7020,15 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7016,13 +7054,13 @@
         <v>100</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7072,7 +7110,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7093,15 +7131,15 @@
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7124,16 +7162,16 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7183,7 +7221,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7192,27 +7230,27 @@
         <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7318,10 +7356,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7429,10 +7467,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7458,13 +7496,13 @@
         <v>100</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7514,7 +7552,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7523,7 +7561,7 @@
         <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
@@ -7535,15 +7573,15 @@
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7569,13 +7607,13 @@
         <v>128</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7604,10 +7642,10 @@
         <v>150</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>76</v>
@@ -7625,7 +7663,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7646,15 +7684,15 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7677,16 +7715,16 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7736,7 +7774,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7745,7 +7783,7 @@
         <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>98</v>
@@ -7757,15 +7795,15 @@
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7791,13 +7829,13 @@
         <v>100</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7847,7 +7885,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7868,15 +7906,15 @@
         <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7899,16 +7937,16 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7934,13 +7972,13 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>76</v>
@@ -7958,7 +7996,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7967,27 +8005,27 @@
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8010,15 +8048,17 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8067,7 +8107,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8076,27 +8116,27 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8119,13 +8159,13 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8176,7 +8216,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8185,7 +8225,7 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>98</v>
@@ -8197,15 +8237,15 @@
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8311,10 +8351,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8340,10 +8380,10 @@
         <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8385,7 +8425,7 @@
         <v>111</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>385</v>
+        <v>112</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>76</v>
@@ -8420,13 +8460,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>76</v>
@@ -8448,16 +8488,16 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8516,7 +8556,7 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>392</v>
+        <v>76</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>115</v>
@@ -8533,13 +8573,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>76</v>
@@ -8561,13 +8601,13 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8627,7 +8667,7 @@
         <v>78</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>392</v>
+        <v>76</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>115</v>
@@ -8644,14 +8684,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8673,16 +8713,16 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8731,7 +8771,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8752,15 +8792,15 @@
         <v>76</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8786,13 +8826,13 @@
         <v>100</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8842,7 +8882,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -8851,7 +8891,7 @@
         <v>86</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>98</v>
@@ -8863,15 +8903,15 @@
         <v>76</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8894,15 +8934,17 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -8951,7 +8993,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -8960,19 +9002,19 @@
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>76</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-Reply.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-Reply.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -496,13 +496,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Communication.meta.tag</t>
   </si>
   <si>
@@ -672,9 +665,6 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -688,9 +678,6 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -732,14 +719,7 @@
     <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.basedOn.id</t>
@@ -836,9 +816,6 @@
     <t>Part of this action.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -914,9 +891,6 @@
     <t>Event.statusReason</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -969,9 +943,6 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1249,6 +1220,9 @@
     <t>An Extension</t>
   </si>
   <si>
+    <t>Erweiterungen werden immer (mindestens) nach url gesliced.</t>
+  </si>
+  <si>
     <t>Communication.payload.extension:OfferedSupplyOptions</t>
   </si>
   <si>
@@ -1268,6 +1242,10 @@
     <t>Sowohl Patient als auch Apotheke können ihre Lieferoptionen oder Angebote für die Abgabe von Medikamenten angeben.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Communication.payload.extension:AvailabilityStatus</t>
   </si>
   <si>
@@ -1323,13 +1301,7 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>Event.note</t>
-  </si>
-  <si>
-    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1677,7 +1649,7 @@
     <col min="26" max="26" width="52.72265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="49.6328125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.7421875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1686,7 +1658,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3010,7 +2982,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>98</v>
@@ -3022,15 +2994,15 @@
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3056,13 +3028,13 @@
         <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3088,31 +3060,31 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3121,7 +3093,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>98</v>
@@ -3133,15 +3105,15 @@
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3167,13 +3139,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3223,7 +3195,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3249,10 +3221,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3275,16 +3247,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3310,31 +3282,31 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3360,14 +3332,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3386,16 +3358,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3445,7 +3417,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3466,19 +3438,19 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3497,16 +3469,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3556,7 +3528,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3577,15 +3549,15 @@
         <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3614,7 +3586,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3655,19 +3627,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3688,15 +3660,15 @@
         <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3722,16 +3694,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3768,19 +3740,19 @@
         <v>76</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3801,15 +3773,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3832,19 +3804,19 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3893,7 +3865,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3902,27 +3874,27 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>210</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3945,17 +3917,15 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -4004,7 +3974,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4019,21 +3989,21 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4059,13 +4029,13 @@
         <v>128</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4115,7 +4085,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4130,25 +4100,25 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4167,16 +4137,16 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4226,7 +4196,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4235,27 +4205,27 @@
         <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4361,10 +4331,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4472,10 +4442,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4501,13 +4471,13 @@
         <v>100</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4557,7 +4527,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4566,7 +4536,7 @@
         <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>98</v>
@@ -4578,15 +4548,15 @@
         <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4612,13 +4582,13 @@
         <v>128</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4647,10 +4617,10 @@
         <v>150</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4668,7 +4638,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4689,15 +4659,15 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4720,16 +4690,16 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4779,7 +4749,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4788,7 +4758,7 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>98</v>
@@ -4800,15 +4770,15 @@
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4834,13 +4804,13 @@
         <v>100</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4890,7 +4860,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4911,19 +4881,19 @@
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4942,17 +4912,15 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -5001,7 +4969,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5010,27 +4978,27 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5053,17 +5021,15 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5112,7 +5078,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5121,10 +5087,10 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>76</v>
@@ -5133,15 +5099,15 @@
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5164,16 +5130,16 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5181,7 +5147,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>76</v>
@@ -5199,13 +5165,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5223,7 +5189,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>86</v>
@@ -5238,10 +5204,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5249,14 +5215,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5275,16 +5241,16 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5310,13 +5276,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5334,7 +5300,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5343,27 +5309,27 @@
         <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>286</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5386,16 +5352,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5421,13 +5387,13 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5445,7 +5411,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5454,7 +5420,7 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>98</v>
@@ -5463,18 +5429,18 @@
         <v>76</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>286</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5497,23 +5463,23 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q35" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="R35" t="s" s="2">
         <v>76</v>
@@ -5534,13 +5500,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5558,7 +5524,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5576,7 +5542,7 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>76</v>
@@ -5584,10 +5550,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5610,17 +5576,15 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -5645,13 +5609,13 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5669,7 +5633,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5678,7 +5642,7 @@
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>98</v>
@@ -5690,19 +5654,19 @@
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>286</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5721,17 +5685,15 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5780,7 +5742,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5789,27 +5751,27 @@
         <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5832,16 +5794,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5867,13 +5829,13 @@
         <v>76</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>76</v>
@@ -5891,7 +5853,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5900,7 +5862,7 @@
         <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>98</v>
@@ -5909,18 +5871,18 @@
         <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>286</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5943,16 +5905,16 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6002,7 +5964,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6011,27 +5973,27 @@
         <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6054,16 +6016,16 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6113,7 +6075,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6122,27 +6084,27 @@
         <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6165,16 +6127,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6224,7 +6186,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6239,10 +6201,10 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6250,10 +6212,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6276,16 +6238,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6335,7 +6297,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6350,10 +6312,10 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6361,10 +6323,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6387,16 +6349,16 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6446,7 +6408,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6455,27 +6417,27 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6581,10 +6543,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6692,10 +6654,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6721,13 +6683,13 @@
         <v>100</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6777,7 +6739,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6786,7 +6748,7 @@
         <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>98</v>
@@ -6798,15 +6760,15 @@
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6832,13 +6794,13 @@
         <v>128</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6867,10 +6829,10 @@
         <v>150</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6888,7 +6850,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6909,15 +6871,15 @@
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6940,16 +6902,16 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6999,7 +6961,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7008,7 +6970,7 @@
         <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
@@ -7020,15 +6982,15 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7054,13 +7016,13 @@
         <v>100</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7110,7 +7072,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7131,15 +7093,15 @@
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7162,16 +7124,16 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7221,7 +7183,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7230,27 +7192,27 @@
         <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7356,10 +7318,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7467,10 +7429,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7496,13 +7458,13 @@
         <v>100</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7552,7 +7514,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7561,7 +7523,7 @@
         <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
@@ -7573,15 +7535,15 @@
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7607,13 +7569,13 @@
         <v>128</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7642,10 +7604,10 @@
         <v>150</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>76</v>
@@ -7663,7 +7625,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7684,15 +7646,15 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7715,16 +7677,16 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7774,7 +7736,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7783,7 +7745,7 @@
         <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>98</v>
@@ -7795,15 +7757,15 @@
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7829,13 +7791,13 @@
         <v>100</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7885,7 +7847,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7906,15 +7868,15 @@
         <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7937,16 +7899,16 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7972,13 +7934,13 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>76</v>
@@ -7996,7 +7958,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8005,27 +7967,27 @@
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8048,17 +8010,15 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8107,7 +8067,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8116,27 +8076,27 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8159,13 +8119,13 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8216,7 +8176,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8225,7 +8185,7 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>98</v>
@@ -8237,15 +8197,15 @@
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8351,10 +8311,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8380,10 +8340,10 @@
         <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8425,7 +8385,7 @@
         <v>111</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>112</v>
+        <v>385</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>76</v>
@@ -8460,13 +8420,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>76</v>
@@ -8488,16 +8448,16 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8556,7 +8516,7 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>76</v>
+        <v>392</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>115</v>
@@ -8573,13 +8533,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>76</v>
@@ -8601,13 +8561,13 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8667,7 +8627,7 @@
         <v>78</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>76</v>
+        <v>392</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>115</v>
@@ -8684,14 +8644,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8713,16 +8673,16 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8771,7 +8731,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8792,15 +8752,15 @@
         <v>76</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8826,13 +8786,13 @@
         <v>100</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8882,7 +8842,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -8891,7 +8851,7 @@
         <v>86</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>98</v>
@@ -8903,15 +8863,15 @@
         <v>76</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8934,17 +8894,15 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -8993,7 +8951,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9002,19 +8960,19 @@
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>419</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
